--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_atacama.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_atacama.xlsx
@@ -404,7 +404,7 @@
         <v>27.95419326031571</v>
       </c>
       <c r="D2">
-        <v>1.817992264472281</v>
+        <v>3.696647032170367</v>
       </c>
       <c r="E2">
         <v>17.45196163708867</v>
@@ -429,7 +429,7 @@
         <v>27.29958095761489</v>
       </c>
       <c r="D3">
-        <v>1.662896961389079</v>
+        <v>3.045397489539749</v>
       </c>
       <c r="E3">
         <v>20.50534082621938</v>
@@ -454,7 +454,7 @@
         <v>31.97440151694714</v>
       </c>
       <c r="D4">
-        <v>1.712951684937069</v>
+        <v>3.787253141831239</v>
       </c>
       <c r="E4">
         <v>16.67165519305597</v>
@@ -479,7 +479,7 @@
         <v>29.80265358456907</v>
       </c>
       <c r="D5">
-        <v>1.5461127391829</v>
+        <v>2.8673273657289</v>
       </c>
       <c r="E5">
         <v>21.17806364251862</v>
@@ -504,7 +504,7 @@
         <v>28.89711838907534</v>
       </c>
       <c r="D6">
-        <v>1.851510606385258</v>
+        <v>3.982027649769585</v>
       </c>
       <c r="E6">
         <v>16.30598136459272</v>
@@ -529,7 +529,7 @@
         <v>28.44964640096486</v>
       </c>
       <c r="D7">
-        <v>1.580059768721036</v>
+        <v>2.870338316286388</v>
       </c>
       <c r="E7">
         <v>21.335884910443</v>
@@ -554,7 +554,7 @@
         <v>26.85768261964736</v>
       </c>
       <c r="D8">
-        <v>1.373108517077388</v>
+        <v>2.175342465753425</v>
       </c>
       <c r="E8">
         <v>26.59865184915285</v>
@@ -579,7 +579,7 @@
         <v>29.76167027772306</v>
       </c>
       <c r="D9">
-        <v>1.472874963736583</v>
+        <v>2.622417355371901</v>
       </c>
       <c r="E9">
         <v>22.71234162365087</v>
@@ -604,7 +604,7 @@
         <v>28.13599062133646</v>
       </c>
       <c r="D10">
-        <v>1.502054392486793</v>
+        <v>2.601491019993223</v>
       </c>
       <c r="E10">
         <v>23.07632155145448</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_atacama.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_atacama.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.95419326031571</v>
+      </c>
+      <c r="C2">
         <v>27.05154133725562</v>
-      </c>
-      <c r="C2">
-        <v>27.95419326031571</v>
       </c>
       <c r="D2">
         <v>3.696647032170367</v>
       </c>
       <c r="E2">
+        <v>18.03429617161642</v>
+      </c>
+      <c r="F2">
+        <v>64.51374219129492</v>
+      </c>
+      <c r="G2">
         <v>17.45196163708867</v>
-      </c>
-      <c r="F2">
-        <v>64.51374219129491</v>
-      </c>
-      <c r="G2">
-        <v>18.03429617161641</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.29958095761489</v>
+      </c>
+      <c r="C3">
         <v>32.83643607886241</v>
-      </c>
-      <c r="C3">
-        <v>27.29958095761489</v>
       </c>
       <c r="D3">
         <v>3.045397489539749</v>
       </c>
       <c r="E3">
+        <v>17.04774569945519</v>
+      </c>
+      <c r="F3">
+        <v>62.44691347432542</v>
+      </c>
+      <c r="G3">
         <v>20.50534082621938</v>
-      </c>
-      <c r="F3">
-        <v>62.44691347432543</v>
-      </c>
-      <c r="G3">
-        <v>17.0477456994552</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>31.97440151694714</v>
+      </c>
+      <c r="C4">
         <v>26.40436122303863</v>
-      </c>
-      <c r="C4">
-        <v>31.97440151694714</v>
       </c>
       <c r="D4">
         <v>3.787253141831239</v>
       </c>
       <c r="E4">
+        <v>20.18856629751571</v>
+      </c>
+      <c r="F4">
+        <v>63.1397785094283</v>
+      </c>
+      <c r="G4">
         <v>16.67165519305597</v>
-      </c>
-      <c r="F4">
-        <v>63.13977850942832</v>
-      </c>
-      <c r="G4">
-        <v>20.18856629751571</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>29.80265358456907</v>
+      </c>
+      <c r="C5">
         <v>34.87568290779351</v>
-      </c>
-      <c r="C5">
-        <v>29.80265358456907</v>
       </c>
       <c r="D5">
         <v>2.8673273657289</v>
       </c>
       <c r="E5">
-        <v>21.17806364251862</v>
+        <v>18.09749492213947</v>
       </c>
       <c r="F5">
         <v>60.72444143534191</v>
       </c>
       <c r="G5">
-        <v>18.09749492213947</v>
+        <v>21.17806364251862</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.89711838907534</v>
+      </c>
+      <c r="C6">
         <v>25.11283416271265</v>
-      </c>
-      <c r="C6">
-        <v>28.89711838907534</v>
       </c>
       <c r="D6">
         <v>3.982027649769585</v>
       </c>
       <c r="E6">
-        <v>16.30598136459272</v>
+        <v>18.76314998497145</v>
       </c>
       <c r="F6">
         <v>64.93086865043583</v>
       </c>
       <c r="G6">
-        <v>18.76314998497145</v>
+        <v>16.30598136459272</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>28.44964640096486</v>
+      </c>
+      <c r="C7">
         <v>34.83909873362206</v>
-      </c>
-      <c r="C7">
-        <v>28.44964640096486</v>
       </c>
       <c r="D7">
         <v>2.870338316286388</v>
       </c>
       <c r="E7">
-        <v>21.335884910443</v>
+        <v>17.42290711923587</v>
       </c>
       <c r="F7">
         <v>61.24120797032113</v>
       </c>
       <c r="G7">
-        <v>17.42290711923587</v>
+        <v>21.335884910443</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>26.85768261964736</v>
+      </c>
+      <c r="C8">
         <v>45.96977329974811</v>
-      </c>
-      <c r="C8">
-        <v>26.85768261964736</v>
       </c>
       <c r="D8">
         <v>2.175342465753425</v>
       </c>
       <c r="E8">
-        <v>26.59865184915285</v>
+        <v>15.5401712515941</v>
       </c>
       <c r="F8">
         <v>57.86117689925305</v>
       </c>
       <c r="G8">
-        <v>15.5401712515941</v>
+        <v>26.59865184915285</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>29.76167027772306</v>
+      </c>
+      <c r="C9">
         <v>38.13275556430963</v>
-      </c>
-      <c r="C9">
-        <v>29.76167027772306</v>
       </c>
       <c r="D9">
         <v>2.622417355371901</v>
       </c>
       <c r="E9">
-        <v>22.71234162365087</v>
+        <v>17.72641952135148</v>
       </c>
       <c r="F9">
         <v>59.56123885499765</v>
       </c>
       <c r="G9">
-        <v>17.72641952135148</v>
+        <v>22.71234162365087</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.13599062133646</v>
+      </c>
+      <c r="C10">
         <v>38.43949459424254</v>
-      </c>
-      <c r="C10">
-        <v>28.13599062133646</v>
       </c>
       <c r="D10">
         <v>2.601491019993223</v>
       </c>
       <c r="E10">
-        <v>23.07632155145448</v>
+        <v>16.89083515796058</v>
       </c>
       <c r="F10">
         <v>60.03284329058491</v>
       </c>
       <c r="G10">
-        <v>16.89083515796058</v>
+        <v>23.07632155145448</v>
       </c>
     </row>
   </sheetData>
